--- a/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-AbridgedMortalityTable-GKS-1986-1987.xlsx
+++ b/population-projection/src/main/resources/mortality_tables/RSFSR/RSFSR-AbridgedMortalityTable-GKS-1986-1987.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\WINAPPS\SLOVO\UKR\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\population-projection\src\main\resources\mortality_tables\RSFSR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56407489-2F90-4A11-93CA-6E8D7B850124}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11A4F03B-F057-46B3-AE6E-163FBA62FDF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-60" windowWidth="38520" windowHeight="23700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="10" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="35">
   <si>
     <t>возраст</t>
   </si>
@@ -126,6 +126,15 @@
   <si>
     <t>Госкомстат СССР, "Таблицы смертности и ожидаемой продолжительности жизни населения", 1989, стр. 235-239.</t>
   </si>
+  <si>
+    <t>Внимание!!!</t>
+  </si>
+  <si>
+    <t>Значения qx относятся не к году в среднем,</t>
+  </si>
+  <si>
+    <t>а ко всей (пятилетней) корзине в целом.</t>
+  </si>
 </sst>
 </file>
 
@@ -134,7 +143,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -143,6 +152,12 @@
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -185,23 +200,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -414,17 +430,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2487394-9CB7-4E6B-B7D4-588501280841}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" t="s">
         <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="6" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -435,14 +466,14 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,7 +499,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -494,7 +525,7 @@
         <v>70.13</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -520,7 +551,7 @@
         <v>70.510000000000005</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -546,7 +577,7 @@
         <v>69.66</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -572,7 +603,7 @@
         <v>68.739999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -598,7 +629,7 @@
         <v>67.790000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -624,7 +655,7 @@
         <v>66.83</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -650,7 +681,7 @@
         <v>62.01</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -676,7 +707,7 @@
         <v>57.15</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -702,7 +733,7 @@
         <v>52.39</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -728,7 +759,7 @@
         <v>47.74</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -754,7 +785,7 @@
         <v>43.12</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -780,7 +811,7 @@
         <v>38.56</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -806,7 +837,7 @@
         <v>34.08</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -832,7 +863,7 @@
         <v>29.76</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -858,7 +889,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -884,7 +915,7 @@
         <v>21.76</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -910,7 +941,7 @@
         <v>18.16</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -936,7 +967,7 @@
         <v>14.75</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -962,7 +993,7 @@
         <v>11.68</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -988,7 +1019,7 @@
         <v>8.99</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -1014,7 +1045,7 @@
         <v>6.73</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -1048,14 +1079,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1112,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1107,7 +1138,7 @@
         <v>65.38</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1133,7 +1164,7 @@
         <v>65.84</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1159,7 +1190,7 @@
         <v>64.959999999999994</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1185,7 +1216,7 @@
         <v>64.02</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1211,7 +1242,7 @@
         <v>63.06</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1237,7 +1268,7 @@
         <v>62.1</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1263,7 +1294,7 @@
         <v>57.29</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1289,7 +1320,7 @@
         <v>52.43</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1315,7 +1346,7 @@
         <v>47.73</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1341,7 +1372,7 @@
         <v>43.13</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1367,7 +1398,7 @@
         <v>38.54</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -1393,7 +1424,7 @@
         <v>34.07</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -1419,7 +1450,7 @@
         <v>29.69</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -1445,7 +1476,7 @@
         <v>25.52</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -1471,7 +1502,7 @@
         <v>21.59</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -1497,7 +1528,7 @@
         <v>17.96</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -1523,7 +1554,7 @@
         <v>14.73</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -1549,7 +1580,7 @@
         <v>12.01</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -1575,7 +1606,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1601,7 +1632,7 @@
         <v>7.3</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -1627,7 +1658,7 @@
         <v>5.42</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -1661,14 +1692,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1694,7 +1725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -1720,7 +1751,7 @@
         <v>74.44</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -1746,7 +1777,7 @@
         <v>74.63</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -1772,7 +1803,7 @@
         <v>73.739999999999995</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -1798,7 +1829,7 @@
         <v>72.8</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -1824,7 +1855,7 @@
         <v>71.83</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1850,7 +1881,7 @@
         <v>70.86</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1876,7 +1907,7 @@
         <v>65.98</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1902,7 +1933,7 @@
         <v>61.07</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1928,7 +1959,7 @@
         <v>56.2</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1954,7 +1985,7 @@
         <v>51.34</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -1980,7 +2011,7 @@
         <v>46.49</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2006,7 +2037,7 @@
         <v>41.69</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2032,7 +2063,7 @@
         <v>36.94</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2058,7 +2089,7 @@
         <v>32.299999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -2084,7 +2115,7 @@
         <v>27.77</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -2110,7 +2141,7 @@
         <v>23.42</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2136,7 +2167,7 @@
         <v>19.29</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -2162,7 +2193,7 @@
         <v>15.34</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2188,7 +2219,7 @@
         <v>11.89</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2214,7 +2245,7 @@
         <v>8.98</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -2240,7 +2271,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -2274,14 +2305,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2307,7 +2338,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2333,7 +2364,7 @@
         <v>70.319999999999993</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -2359,7 +2390,7 @@
         <v>70.67</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2385,7 +2416,7 @@
         <v>69.790000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -2411,7 +2442,7 @@
         <v>68.849999999999994</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -2437,7 +2468,7 @@
         <v>67.89</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -2463,7 +2494,7 @@
         <v>66.92</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -2489,7 +2520,7 @@
         <v>62.08</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -2515,7 +2546,7 @@
         <v>57.2</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -2541,7 +2572,7 @@
         <v>52.42</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2567,7 +2598,7 @@
         <v>47.71</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -2593,7 +2624,7 @@
         <v>43.01</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -2619,7 +2650,7 @@
         <v>38.4</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -2645,7 +2676,7 @@
         <v>33.869999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -2671,7 +2702,7 @@
         <v>29.49</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -2697,7 +2728,7 @@
         <v>25.31</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -2723,7 +2754,7 @@
         <v>21.37</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -2749,7 +2780,7 @@
         <v>17.73</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -2775,7 +2806,7 @@
         <v>14.27</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -2801,7 +2832,7 @@
         <v>11.19</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2827,7 +2858,7 @@
         <v>8.5500000000000007</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -2853,7 +2884,7 @@
         <v>6.35</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -2887,14 +2918,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2920,7 +2951,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2946,7 +2977,7 @@
         <v>63.21</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -2972,7 +3003,7 @@
         <v>63.72</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -2998,7 +3029,7 @@
         <v>62.96</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -3024,7 +3055,7 @@
         <v>62.07</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3050,7 +3081,7 @@
         <v>61.16</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3076,7 +3107,7 @@
         <v>60.22</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -3102,7 +3133,7 @@
         <v>55.49</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -3128,7 +3159,7 @@
         <v>50.68</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -3154,7 +3185,7 @@
         <v>46.04</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -3180,7 +3211,7 @@
         <v>41.81</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -3206,7 +3237,7 @@
         <v>37.729999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -3232,7 +3263,7 @@
         <v>33.57</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -3258,7 +3289,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -3284,7 +3315,7 @@
         <v>25.64</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -3310,7 +3341,7 @@
         <v>22.01</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -3336,7 +3367,7 @@
         <v>18.579999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -3362,7 +3393,7 @@
         <v>15.46</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -3388,7 +3419,7 @@
         <v>12.74</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -3414,7 +3445,7 @@
         <v>10.29</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -3440,7 +3471,7 @@
         <v>8.1300000000000008</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -3466,7 +3497,7 @@
         <v>6.27</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -3500,14 +3531,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3533,7 +3564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -3559,7 +3590,7 @@
         <v>74.400000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -3585,7 +3616,7 @@
         <v>74.73</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -3611,7 +3642,7 @@
         <v>73.97</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -3637,7 +3668,7 @@
         <v>73.069999999999993</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -3663,7 +3694,7 @@
         <v>72.14</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -3689,7 +3720,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -3715,7 +3746,7 @@
         <v>66.38</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -3741,7 +3772,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -3767,7 +3798,7 @@
         <v>56.71</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -3793,7 +3824,7 @@
         <v>51.98</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -3819,7 +3850,7 @@
         <v>47.26</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -3845,7 +3876,7 @@
         <v>42.57</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -3871,7 +3902,7 @@
         <v>37.94</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -3897,7 +3928,7 @@
         <v>33.42</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -3923,7 +3954,7 @@
         <v>29.02</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -3949,7 +3980,7 @@
         <v>24.78</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -3975,7 +4006,7 @@
         <v>20.71</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -4001,7 +4032,7 @@
         <v>16.850000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -4027,7 +4058,7 @@
         <v>13.35</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -4053,7 +4084,7 @@
         <v>10.26</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -4079,7 +4110,7 @@
         <v>7.63</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -4113,14 +4144,14 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4146,7 +4177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -4172,7 +4203,7 @@
         <v>69.09</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -4198,7 +4229,7 @@
         <v>69.540000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4224,7 +4255,7 @@
         <v>68.78</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4250,7 +4281,7 @@
         <v>67.89</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4276,7 +4307,7 @@
         <v>66.97</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -4302,7 +4333,7 @@
         <v>66.03</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -4328,7 +4359,7 @@
         <v>61.26</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -4354,7 +4385,7 @@
         <v>56.42</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -4380,7 +4411,7 @@
         <v>51.74</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -4406,7 +4437,7 @@
         <v>47.3</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -4432,7 +4463,7 @@
         <v>42.98</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -4458,7 +4489,7 @@
         <v>38.61</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -4484,7 +4515,7 @@
         <v>34.33</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -4510,7 +4541,7 @@
         <v>30.2</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -4536,7 +4567,7 @@
         <v>26.26</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -4562,7 +4593,7 @@
         <v>22.51</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -4588,7 +4619,7 @@
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -4614,7 +4645,7 @@
         <v>15.65</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -4640,7 +4671,7 @@
         <v>12.55</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -4666,7 +4697,7 @@
         <v>9.77</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -4692,7 +4723,7 @@
         <v>7.36</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -4726,14 +4757,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4759,7 +4790,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -4785,7 +4816,7 @@
         <v>64.91</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -4811,7 +4842,7 @@
         <v>65.39</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -4837,7 +4868,7 @@
         <v>64.540000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -4863,7 +4894,7 @@
         <v>63.62</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -4889,7 +4920,7 @@
         <v>62.68</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -4915,7 +4946,7 @@
         <v>61.73</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -4941,7 +4972,7 @@
         <v>56.94</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -4967,7 +4998,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -4993,7 +5024,7 @@
         <v>47.41</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -5019,7 +5050,7 @@
         <v>42.9</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -5045,7 +5076,7 @@
         <v>38.42</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -5071,7 +5102,7 @@
         <v>34.01</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -5097,7 +5128,7 @@
         <v>29.7</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -5123,7 +5154,7 @@
         <v>25.6</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -5149,7 +5180,7 @@
         <v>21.75</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -5175,7 +5206,7 @@
         <v>18.18</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -5201,7 +5232,7 @@
         <v>14.98</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -5227,7 +5258,7 @@
         <v>12.24</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -5253,7 +5284,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -5279,7 +5310,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -5305,7 +5336,7 @@
         <v>5.73</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -5339,14 +5370,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5372,7 +5403,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -5398,7 +5429,7 @@
         <v>74.55</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
@@ -5424,7 +5455,7 @@
         <v>74.78</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2" t="s">
         <v>10</v>
       </c>
@@ -5450,7 +5481,7 @@
         <v>73.930000000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -5476,7 +5507,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2" t="s">
         <v>12</v>
       </c>
@@ -5502,7 +5533,7 @@
         <v>72.05</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -5528,7 +5559,7 @@
         <v>71.09</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -5554,7 +5585,7 @@
         <v>66.23</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -5580,7 +5611,7 @@
         <v>61.33</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="2" t="s">
         <v>16</v>
       </c>
@@ -5606,7 +5637,7 @@
         <v>56.47</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -5632,7 +5663,7 @@
         <v>51.64</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="2" t="s">
         <v>18</v>
       </c>
@@ -5658,7 +5689,7 @@
         <v>46.82</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="2" t="s">
         <v>19</v>
       </c>
@@ -5684,7 +5715,7 @@
         <v>42.04</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="2" t="s">
         <v>20</v>
       </c>
@@ -5710,7 +5741,7 @@
         <v>37.32</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="2" t="s">
         <v>21</v>
       </c>
@@ -5736,7 +5767,7 @@
         <v>32.700000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2" t="s">
         <v>22</v>
       </c>
@@ -5762,7 +5793,7 @@
         <v>28.2</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2" t="s">
         <v>23</v>
       </c>
@@ -5788,7 +5819,7 @@
         <v>23.89</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2" t="s">
         <v>24</v>
       </c>
@@ -5814,7 +5845,7 @@
         <v>19.78</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
@@ -5840,7 +5871,7 @@
         <v>15.88</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="2" t="s">
         <v>26</v>
       </c>
@@ -5866,7 +5897,7 @@
         <v>12.42</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -5892,7 +5923,7 @@
         <v>9.4600000000000009</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -5918,7 +5949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="2" t="s">
         <v>29</v>
       </c>
@@ -5947,4 +5978,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>